--- a/data/trans_orig/P57_AC_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57_AC_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2007</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205872</t>
+          <t>205208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231629</t>
+          <t>231554</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222885</t>
+          <t>223655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243187</t>
+          <t>243473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>435617</t>
+          <t>437373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>468472</t>
+          <t>468676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41381</t>
+          <t>41456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67138</t>
+          <t>67802</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37953</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65376</t>
+          <t>65172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98231</t>
+          <t>96475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>266787</t>
+          <t>266657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311445</t>
+          <t>310743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>311631</t>
+          <t>311580</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>353561</t>
+          <t>352304</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>592135</t>
+          <t>588812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>654849</t>
+          <t>651702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>180546</t>
+          <t>181248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>225204</t>
+          <t>225334</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150388</t>
+          <t>151645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192318</t>
+          <t>192369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>341091</t>
+          <t>344238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>403805</t>
+          <t>407128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178743</t>
+          <t>180313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213932</t>
+          <t>215669</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174814</t>
+          <t>172824</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211575</t>
+          <t>209917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>360776</t>
+          <t>363402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>413709</t>
+          <t>412139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104914</t>
+          <t>103177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140103</t>
+          <t>138533</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123837</t>
+          <t>125495</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160598</t>
+          <t>162588</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240549</t>
+          <t>242119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>293482</t>
+          <t>290856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>236877</t>
+          <t>237490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273144</t>
+          <t>271651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>242248</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275009</t>
+          <t>275361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>489272</t>
+          <t>490752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>537486</t>
+          <t>537645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85527</t>
+          <t>87020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121794</t>
+          <t>121181</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96447</t>
+          <t>96095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129208</t>
+          <t>130473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192641</t>
+          <t>192482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>240855</t>
+          <t>239375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147596</t>
+          <t>148533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172457</t>
+          <t>172632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>167514</t>
+          <t>168274</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187450</t>
+          <t>187300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322693</t>
+          <t>323851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>354729</t>
+          <t>353951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>30676</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55712</t>
+          <t>54775</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20218</t>
+          <t>20368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40154</t>
+          <t>39394</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56247</t>
+          <t>57025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88283</t>
+          <t>87125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>172889</t>
+          <t>172386</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203312</t>
+          <t>203061</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>189759</t>
+          <t>190600</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>218754</t>
+          <t>219080</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>370998</t>
+          <t>371935</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>414382</t>
+          <t>415430</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67499</t>
+          <t>67750</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97922</t>
+          <t>98425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59390</t>
+          <t>59064</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88385</t>
+          <t>87544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134573</t>
+          <t>133525</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177957</t>
+          <t>177020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>295405</t>
+          <t>295509</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>345054</t>
+          <t>347277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>287014</t>
+          <t>286980</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>336087</t>
+          <t>338320</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>599122</t>
+          <t>597082</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>670030</t>
+          <t>671678</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>269973</t>
+          <t>267750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>319622</t>
+          <t>319518</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301152</t>
+          <t>298919</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>350225</t>
+          <t>350259</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>582236</t>
+          <t>580588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>653144</t>
+          <t>655184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>572051</t>
+          <t>568802</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>614624</t>
+          <t>616320</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>655922</t>
+          <t>654439</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>692307</t>
+          <t>693046</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1239585</t>
+          <t>1240130</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1296377</t>
+          <t>1298518</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127621</t>
+          <t>125925</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170194</t>
+          <t>173443</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>90053</t>
+          <t>89314</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>126438</t>
+          <t>127921</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>228228</t>
+          <t>226087</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>285020</t>
+          <t>284475</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2170969</t>
+          <t>2172811</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2275537</t>
+          <t>2281084</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2333250</t>
+          <t>2334164</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2435811</t>
+          <t>2444053</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4539778</t>
+          <t>4540249</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4688116</t>
+          <t>4681898</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>998372</t>
+          <t>992825</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1102940</t>
+          <t>1101098</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>941255</t>
+          <t>933013</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1043816</t>
+          <t>1042902</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1962859</t>
+          <t>1969077</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2111197</t>
+          <t>2110726</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2012</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2012 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>196189</t>
+          <t>195191</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>227996</t>
+          <t>227032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>216698</t>
+          <t>215081</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>244119</t>
+          <t>243801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>420817</t>
+          <t>421786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>463389</t>
+          <t>462964</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62214</t>
+          <t>63178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94021</t>
+          <t>95019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39130</t>
+          <t>39448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66551</t>
+          <t>68168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110070</t>
+          <t>110495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152642</t>
+          <t>151673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>255238</t>
+          <t>254014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>300018</t>
+          <t>301529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274123</t>
+          <t>274284</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>323075</t>
+          <t>320959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>544103</t>
+          <t>541944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>610220</t>
+          <t>610825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,53%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203552</t>
+          <t>202041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248332</t>
+          <t>249556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199495</t>
+          <t>201611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>248447</t>
+          <t>248286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415920</t>
+          <t>415315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>482037</t>
+          <t>484196</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>189704</t>
+          <t>191477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>225354</t>
+          <t>224604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>232909</t>
+          <t>232448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>265896</t>
+          <t>264928</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>431092</t>
+          <t>433905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>480817</t>
+          <t>483062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97665</t>
+          <t>98415</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133315</t>
+          <t>131542</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74138</t>
+          <t>75106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107125</t>
+          <t>107586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182236</t>
+          <t>179991</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231961</t>
+          <t>229148</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171868</t>
+          <t>173150</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>212153</t>
+          <t>212990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216779</t>
+          <t>216114</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>257633</t>
+          <t>256247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>401366</t>
+          <t>399557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>455708</t>
+          <t>455690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,14%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158551</t>
+          <t>157714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198836</t>
+          <t>197554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129336</t>
+          <t>130722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170190</t>
+          <t>170855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301965</t>
+          <t>301983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>356307</t>
+          <t>358116</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,27%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97829</t>
+          <t>96901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127734</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143852</t>
+          <t>142345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170172</t>
+          <t>169491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>248703</t>
+          <t>248328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289145</t>
+          <t>291441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83869</t>
+          <t>83575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113774</t>
+          <t>114702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48526</t>
+          <t>49207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74846</t>
+          <t>76353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141157</t>
+          <t>138861</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181599</t>
+          <t>181974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>148803</t>
+          <t>148724</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>180859</t>
+          <t>183469</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>198061</t>
+          <t>197852</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>226765</t>
+          <t>225907</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>357483</t>
+          <t>355906</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>400551</t>
+          <t>398759</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88978</t>
+          <t>86368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121034</t>
+          <t>121113</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52166</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80870</t>
+          <t>81079</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148217</t>
+          <t>150009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>191285</t>
+          <t>192862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>365151</t>
+          <t>366260</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>420416</t>
+          <t>420229</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>450138</t>
+          <t>448979</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>499661</t>
+          <t>499914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>828409</t>
+          <t>834048</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>901731</t>
+          <t>907471</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234467</t>
+          <t>234654</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>289732</t>
+          <t>288623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>186348</t>
+          <t>186095</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>235871</t>
+          <t>237030</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>439161</t>
+          <t>433421</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>512483</t>
+          <t>506844</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>673848</t>
+          <t>672207</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>709543</t>
+          <t>709547</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>706440</t>
+          <t>708505</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>746118</t>
+          <t>746200</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1393984</t>
+          <t>1393845</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1446204</t>
+          <t>1444292</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65628</t>
+          <t>65624</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>101323</t>
+          <t>102964</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75653</t>
+          <t>75571</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>115331</t>
+          <t>113266</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>150738</t>
+          <t>152650</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>202958</t>
+          <t>203097</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2195742</t>
+          <t>2198487</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2312300</t>
+          <t>2310203</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2536064</t>
+          <t>2540611</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2640140</t>
+          <t>2644727</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4767294</t>
+          <t>4763531</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4924822</t>
+          <t>4918237</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1086697</t>
+          <t>1088794</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1203255</t>
+          <t>1200510</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>898092</t>
+          <t>893505</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1002168</t>
+          <t>997621</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2012407</t>
+          <t>2018992</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2169935</t>
+          <t>2173698</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2016</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2016 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>221130</t>
+          <t>219976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>248363</t>
+          <t>246912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222777</t>
+          <t>222983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>249686</t>
+          <t>250766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>452331</t>
+          <t>451851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>490572</t>
+          <t>491085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38459</t>
+          <t>39910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65692</t>
+          <t>66846</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36106</t>
+          <t>35026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63015</t>
+          <t>62809</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82042</t>
+          <t>81529</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120283</t>
+          <t>120763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>379327</t>
+          <t>379187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>414797</t>
+          <t>415381</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>399756</t>
+          <t>399645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>435842</t>
+          <t>435032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>789484</t>
+          <t>791989</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>840181</t>
+          <t>842035</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83708</t>
+          <t>83124</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119178</t>
+          <t>119318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82801</t>
+          <t>83611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118887</t>
+          <t>118998</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176967</t>
+          <t>175113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227664</t>
+          <t>225159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>210172</t>
+          <t>210532</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>241305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>253182</t>
+          <t>253550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>283081</t>
+          <t>283022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>472967</t>
+          <t>472856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>515804</t>
+          <t>516972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76773</t>
+          <t>76395</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107528</t>
+          <t>107168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50670</t>
+          <t>50729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80569</t>
+          <t>80201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135646</t>
+          <t>134478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178483</t>
+          <t>178594</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151039</t>
+          <t>149593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189323</t>
+          <t>188094</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189209</t>
+          <t>191435</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228525</t>
+          <t>231490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>352279</t>
+          <t>351291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>410434</t>
+          <t>407656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178616</t>
+          <t>179845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>216900</t>
+          <t>218346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156697</t>
+          <t>153732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196013</t>
+          <t>193787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342727</t>
+          <t>345505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>400882</t>
+          <t>401870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>172069</t>
+          <t>171354</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191944</t>
+          <t>190766</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180312</t>
+          <t>180184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>198729</t>
+          <t>199773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>357941</t>
+          <t>358985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>387044</t>
+          <t>385884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19277</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39152</t>
+          <t>39867</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38275</t>
+          <t>38403</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42764</t>
+          <t>43924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71867</t>
+          <t>70823</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>188849</t>
+          <t>189203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>216805</t>
+          <t>216090</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194019</t>
+          <t>194692</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>222022</t>
+          <t>222283</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>390104</t>
+          <t>390022</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>429146</t>
+          <t>429917</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>47033</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74274</t>
+          <t>73920</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49154</t>
+          <t>48893</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77157</t>
+          <t>76484</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105153</t>
+          <t>104382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144195</t>
+          <t>144277</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>516165</t>
+          <t>513407</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>554328</t>
+          <t>556576</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>565361</t>
+          <t>565498</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>602445</t>
+          <t>602826</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1092031</t>
+          <t>1092526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1151083</t>
+          <t>1147481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98727</t>
+          <t>96479</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136890</t>
+          <t>139648</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81947</t>
+          <t>81566</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>119031</t>
+          <t>118894</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>186364</t>
+          <t>189966</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>245416</t>
+          <t>244921</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>701195</t>
+          <t>700091</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>731064</t>
+          <t>731802</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>755022</t>
+          <t>754396</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>784003</t>
+          <t>784110</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1464476</t>
+          <t>1466082</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1506955</t>
+          <t>1507931</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47519</t>
+          <t>46781</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77388</t>
+          <t>78492</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40114</t>
+          <t>40007</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69095</t>
+          <t>69721</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>95745</t>
+          <t>94769</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138224</t>
+          <t>136618</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2618813</t>
+          <t>2620694</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2715505</t>
+          <t>2717371</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2847958</t>
+          <t>2844493</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2934358</t>
+          <t>2937690</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5495187</t>
+          <t>5497943</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5628988</t>
+          <t>5625830</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>661443</t>
+          <t>659577</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>758135</t>
+          <t>756254</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>587322</t>
+          <t>583990</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>673722</t>
+          <t>677187</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1269641</t>
+          <t>1272799</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1403442</t>
+          <t>1400686</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2023</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2023 (tasa de respuesta: 98,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140156</t>
+          <t>139318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184967</t>
+          <t>184430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>157247</t>
+          <t>155092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184606</t>
+          <t>182994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>306190</t>
+          <t>306149</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>357712</t>
+          <t>358970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125736</t>
+          <t>126273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>170547</t>
+          <t>171385</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102586</t>
+          <t>104198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129945</t>
+          <t>132100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>240184</t>
+          <t>238926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291706</t>
+          <t>291747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>299285</t>
+          <t>293993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>354398</t>
+          <t>353412</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>272976</t>
+          <t>274217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>314875</t>
+          <t>313314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>583251</t>
+          <t>580976</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>654376</t>
+          <t>653247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,61%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159539</t>
+          <t>160525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214652</t>
+          <t>219944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>198190</t>
+          <t>199751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240089</t>
+          <t>238848</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>372626</t>
+          <t>373755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>443751</t>
+          <t>446026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119618</t>
+          <t>121539</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156605</t>
+          <t>154293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151562</t>
+          <t>151130</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182159</t>
+          <t>181618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>282443</t>
+          <t>282785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>329357</t>
+          <t>324860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150177</t>
+          <t>152489</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>187164</t>
+          <t>185243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146299</t>
+          <t>146840</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176896</t>
+          <t>177328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>305882</t>
+          <t>310379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352796</t>
+          <t>352454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78882</t>
+          <t>81025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121167</t>
+          <t>121919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80228</t>
+          <t>80601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170482</t>
+          <t>170080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>166823</t>
+          <t>176614</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275033</t>
+          <t>273690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187247</t>
+          <t>186495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229532</t>
+          <t>227389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295149</t>
+          <t>295551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385403</t>
+          <t>385030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>499012</t>
+          <t>500355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>607222</t>
+          <t>597431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156046</t>
+          <t>155691</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169538</t>
+          <t>170231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185170</t>
+          <t>185531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197359</t>
+          <t>197280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>345492</t>
+          <t>345129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364766</t>
+          <t>364362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22012</t>
+          <t>22367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>22743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21566</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40840</t>
+          <t>41203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89725</t>
+          <t>91322</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>117512</t>
+          <t>118096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90460</t>
+          <t>90361</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113192</t>
+          <t>115085</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>188072</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>225378</t>
+          <t>222822</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151659</t>
+          <t>151075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179446</t>
+          <t>177849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>143471</t>
+          <t>141578</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166203</t>
+          <t>166302</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>300456</t>
+          <t>303012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>337762</t>
+          <t>338621</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>347429</t>
+          <t>347120</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>405750</t>
+          <t>406737</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>374730</t>
+          <t>372366</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>420382</t>
+          <t>421367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>737221</t>
+          <t>735601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>811490</t>
+          <t>812529</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>209558</t>
+          <t>208571</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>267879</t>
+          <t>268188</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>211579</t>
+          <t>210594</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>257231</t>
+          <t>259595</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>435778</t>
+          <t>434739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>510047</t>
+          <t>511667</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>255337</t>
+          <t>261141</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>790986</t>
+          <t>794057</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>608732</t>
+          <t>608526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>640088</t>
+          <t>640598</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>747166</t>
+          <t>738102</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1420939</t>
+          <t>1424370</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>135072</t>
+          <t>132001</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>670721</t>
+          <t>664917</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76544</t>
+          <t>76034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107900</t>
+          <t>108106</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>221752</t>
+          <t>218321</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>895525</t>
+          <t>904589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1473323</t>
+          <t>1502962</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2122379</t>
+          <t>2115993</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1927645</t>
+          <t>1933782</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2155887</t>
+          <t>2152435</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3468951</t>
+          <t>3540564</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4218069</t>
+          <t>4221190</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1306052</t>
+          <t>1312438</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1955108</t>
+          <t>1925469</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1251989</t>
+          <t>1255441</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1480231</t>
+          <t>1474094</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2618238</t>
+          <t>2615117</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3367356</t>
+          <t>3295743</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_AC_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57_AC_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205208</t>
+          <t>205363</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231554</t>
+          <t>229362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>223655</t>
+          <t>223581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243473</t>
+          <t>242671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>437373</t>
+          <t>436413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>468676</t>
+          <t>469569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41456</t>
+          <t>43648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67802</t>
+          <t>67647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37183</t>
+          <t>37257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65172</t>
+          <t>64279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96475</t>
+          <t>97435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>266657</t>
+          <t>265500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>310743</t>
+          <t>309561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>311580</t>
+          <t>314437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>352304</t>
+          <t>353871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>588812</t>
+          <t>593946</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>651702</t>
+          <t>653690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181248</t>
+          <t>182430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>225334</t>
+          <t>226491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151645</t>
+          <t>150078</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192369</t>
+          <t>189512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344238</t>
+          <t>342250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>407128</t>
+          <t>401994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>180313</t>
+          <t>179188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215669</t>
+          <t>214658</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172824</t>
+          <t>172801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>209917</t>
+          <t>208643</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>363402</t>
+          <t>364238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>412139</t>
+          <t>413320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103177</t>
+          <t>104188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138533</t>
+          <t>139658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125495</t>
+          <t>126769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162588</t>
+          <t>162611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242119</t>
+          <t>240938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>290856</t>
+          <t>290020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>237490</t>
+          <t>237845</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>271651</t>
+          <t>271568</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>238363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275361</t>
+          <t>274547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>490752</t>
+          <t>487600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>537645</t>
+          <t>533206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87020</t>
+          <t>87103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121181</t>
+          <t>120826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96095</t>
+          <t>96909</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130473</t>
+          <t>133093</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192482</t>
+          <t>196921</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239375</t>
+          <t>242527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148533</t>
+          <t>149272</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172632</t>
+          <t>172567</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168274</t>
+          <t>167119</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187300</t>
+          <t>188053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323851</t>
+          <t>323239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>353951</t>
+          <t>353919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30676</t>
+          <t>30741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54775</t>
+          <t>54036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39394</t>
+          <t>40549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57025</t>
+          <t>57057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87125</t>
+          <t>87737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>172386</t>
+          <t>171002</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203061</t>
+          <t>202257</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>190600</t>
+          <t>189424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>219080</t>
+          <t>218680</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>371935</t>
+          <t>372982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>415430</t>
+          <t>414357</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67750</t>
+          <t>68554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98425</t>
+          <t>99809</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59064</t>
+          <t>59464</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87544</t>
+          <t>88720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133525</t>
+          <t>134598</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177020</t>
+          <t>175973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>295509</t>
+          <t>295391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>347277</t>
+          <t>344860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>286980</t>
+          <t>286927</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>338320</t>
+          <t>337909</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>597082</t>
+          <t>598299</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>671678</t>
+          <t>671882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>267750</t>
+          <t>270167</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>319518</t>
+          <t>319636</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298919</t>
+          <t>299330</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>350259</t>
+          <t>350312</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>580588</t>
+          <t>580384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>655184</t>
+          <t>653967</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,22%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>568802</t>
+          <t>571335</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>616320</t>
+          <t>614403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>654439</t>
+          <t>654738</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>693046</t>
+          <t>691161</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1240130</t>
+          <t>1238884</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1298518</t>
+          <t>1296021</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125925</t>
+          <t>127842</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>173443</t>
+          <t>170910</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89314</t>
+          <t>91199</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>127921</t>
+          <t>127622</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>226087</t>
+          <t>228584</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>284475</t>
+          <t>285721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2172811</t>
+          <t>2179290</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2281084</t>
+          <t>2280419</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2334164</t>
+          <t>2336294</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2444053</t>
+          <t>2438619</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4540249</t>
+          <t>4532346</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4681898</t>
+          <t>4684354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>992825</t>
+          <t>993490</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1101098</t>
+          <t>1094619</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>933013</t>
+          <t>938447</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1042902</t>
+          <t>1040772</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1969077</t>
+          <t>1966621</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2110726</t>
+          <t>2118629</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>195191</t>
+          <t>194490</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>227032</t>
+          <t>227892</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>215081</t>
+          <t>216924</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243801</t>
+          <t>244568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>421786</t>
+          <t>421590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>462964</t>
+          <t>462262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63178</t>
+          <t>62318</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95019</t>
+          <t>95720</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39448</t>
+          <t>38681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68168</t>
+          <t>66325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110495</t>
+          <t>111197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151673</t>
+          <t>151869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>254014</t>
+          <t>255340</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>301529</t>
+          <t>301799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274284</t>
+          <t>274991</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>320959</t>
+          <t>322750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>541944</t>
+          <t>543409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>610825</t>
+          <t>610339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202041</t>
+          <t>201771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>249556</t>
+          <t>248230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201611</t>
+          <t>199820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>248286</t>
+          <t>247579</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415315</t>
+          <t>415801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>484196</t>
+          <t>482731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191477</t>
+          <t>190733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>224604</t>
+          <t>225924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>232448</t>
+          <t>231559</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>264928</t>
+          <t>266224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>433905</t>
+          <t>434384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>483062</t>
+          <t>480850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,52%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98415</t>
+          <t>97095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131542</t>
+          <t>132286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75106</t>
+          <t>73810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107586</t>
+          <t>108475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>179991</t>
+          <t>182203</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>229148</t>
+          <t>228669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173150</t>
+          <t>173147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>212990</t>
+          <t>211754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216114</t>
+          <t>218478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256247</t>
+          <t>256032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>399557</t>
+          <t>400223</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>455690</t>
+          <t>457888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,43%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157714</t>
+          <t>158950</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197554</t>
+          <t>197557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130722</t>
+          <t>130937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170855</t>
+          <t>168491</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301983</t>
+          <t>299785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>358116</t>
+          <t>357450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96901</t>
+          <t>98679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>127088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>142345</t>
+          <t>141937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169491</t>
+          <t>168527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>248328</t>
+          <t>248878</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>291441</t>
+          <t>289632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83575</t>
+          <t>84515</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114702</t>
+          <t>112924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49207</t>
+          <t>50171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76353</t>
+          <t>76761</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138861</t>
+          <t>140670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181974</t>
+          <t>181424</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>148724</t>
+          <t>149579</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>183469</t>
+          <t>181264</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>197852</t>
+          <t>195757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>225907</t>
+          <t>226092</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>355906</t>
+          <t>355331</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>398759</t>
+          <t>399964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86368</t>
+          <t>88573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121113</t>
+          <t>120258</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>52839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81079</t>
+          <t>83174</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>150009</t>
+          <t>148804</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>192862</t>
+          <t>193437</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>366260</t>
+          <t>365642</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>420229</t>
+          <t>421101</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>448979</t>
+          <t>451083</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>499914</t>
+          <t>498684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>834048</t>
+          <t>832687</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>907471</t>
+          <t>905385</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234654</t>
+          <t>233782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288623</t>
+          <t>289241</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>186095</t>
+          <t>187325</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>237030</t>
+          <t>234926</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>433421</t>
+          <t>435507</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>506844</t>
+          <t>508205</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>672207</t>
+          <t>673655</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>709547</t>
+          <t>707991</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>708505</t>
+          <t>706554</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>746200</t>
+          <t>744839</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1393845</t>
+          <t>1394105</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1444292</t>
+          <t>1445050</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65624</t>
+          <t>67180</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>102964</t>
+          <t>101516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75571</t>
+          <t>76932</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>113266</t>
+          <t>115217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152650</t>
+          <t>151892</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>203097</t>
+          <t>202837</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2198487</t>
+          <t>2197132</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2310203</t>
+          <t>2310843</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2540611</t>
+          <t>2538399</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2644727</t>
+          <t>2645490</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4763531</t>
+          <t>4769576</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4918237</t>
+          <t>4920842</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1088794</t>
+          <t>1088154</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1200510</t>
+          <t>1201865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>893505</t>
+          <t>892742</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>997621</t>
+          <t>999833</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2018992</t>
+          <t>2016387</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2173698</t>
+          <t>2167653</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>219976</t>
+          <t>220504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>246912</t>
+          <t>248398</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222983</t>
+          <t>225200</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250766</t>
+          <t>251046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>451851</t>
+          <t>455402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>491085</t>
+          <t>491747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>38424</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66846</t>
+          <t>66318</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35026</t>
+          <t>34746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62809</t>
+          <t>60592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81529</t>
+          <t>80867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120763</t>
+          <t>117212</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>379187</t>
+          <t>379205</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>415381</t>
+          <t>414559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>399645</t>
+          <t>399519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>435032</t>
+          <t>436160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>791989</t>
+          <t>788868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>842035</t>
+          <t>842304</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83124</t>
+          <t>83946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119318</t>
+          <t>119300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83611</t>
+          <t>82483</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118998</t>
+          <t>119124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>175113</t>
+          <t>174844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>225159</t>
+          <t>228280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>210532</t>
+          <t>209758</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241305</t>
+          <t>241874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>253550</t>
+          <t>255718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>283022</t>
+          <t>284553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>472856</t>
+          <t>474012</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>516972</t>
+          <t>517120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76395</t>
+          <t>75826</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107168</t>
+          <t>107942</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50729</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80201</t>
+          <t>78033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134478</t>
+          <t>134330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178594</t>
+          <t>177438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149593</t>
+          <t>149096</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>188094</t>
+          <t>190437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>191435</t>
+          <t>189621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>231490</t>
+          <t>231688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>351291</t>
+          <t>350526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>407656</t>
+          <t>410101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179845</t>
+          <t>177502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>218346</t>
+          <t>218843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153732</t>
+          <t>153534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193787</t>
+          <t>195601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345505</t>
+          <t>343060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401870</t>
+          <t>402635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>171354</t>
+          <t>171743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190766</t>
+          <t>190971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180184</t>
+          <t>180660</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199773</t>
+          <t>199726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>358985</t>
+          <t>357948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>385884</t>
+          <t>385130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>20250</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39867</t>
+          <t>39478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18814</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>37927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43924</t>
+          <t>44678</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70823</t>
+          <t>71860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>189203</t>
+          <t>189063</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>216090</t>
+          <t>216040</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194692</t>
+          <t>193102</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>222283</t>
+          <t>221286</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>390022</t>
+          <t>390277</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>429917</t>
+          <t>429757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47033</t>
+          <t>47083</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73920</t>
+          <t>74060</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>49890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76484</t>
+          <t>78074</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104382</t>
+          <t>104542</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144277</t>
+          <t>144022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>513407</t>
+          <t>513172</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>556576</t>
+          <t>554938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>565498</t>
+          <t>565785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>602826</t>
+          <t>602603</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1092526</t>
+          <t>1093787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1147481</t>
+          <t>1148059</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96479</t>
+          <t>98117</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139648</t>
+          <t>139883</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81566</t>
+          <t>81789</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118894</t>
+          <t>118607</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>189966</t>
+          <t>189388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>244921</t>
+          <t>243660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>700091</t>
+          <t>703223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>731802</t>
+          <t>731358</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>754396</t>
+          <t>752222</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>784110</t>
+          <t>781935</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,47 +9830,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>91,28%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>94,88%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1394</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1488611</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>1467134</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>1509188</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>91,54%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1394</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1488611</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1466082</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>1507931</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>91,48%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46781</t>
+          <t>47225</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78492</t>
+          <t>75360</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40007</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69721</t>
+          <t>71895</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,47 +9943,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>8,72%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>114089</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>93512</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>135566</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>8,46%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>114089</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>94769</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>136618</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2620694</t>
+          <t>2625373</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2717371</t>
+          <t>2718147</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2844493</t>
+          <t>2848419</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2937690</t>
+          <t>2940170</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5497943</t>
+          <t>5492814</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5625830</t>
+          <t>5627169</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>659577</t>
+          <t>658801</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>756254</t>
+          <t>751575</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>583990</t>
+          <t>581510</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>677187</t>
+          <t>673261</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1272799</t>
+          <t>1271460</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1400686</t>
+          <t>1405815</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>163338</t>
+          <t>174034</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139318</t>
+          <t>155322</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184430</t>
+          <t>191935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>169638</t>
+          <t>187825</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155092</t>
+          <t>173480</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>182994</t>
+          <t>200682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>332977</t>
+          <t>361859</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>306149</t>
+          <t>338674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>358970</t>
+          <t>386688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>147365</t>
+          <t>144063</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126273</t>
+          <t>126162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>171385</t>
+          <t>162775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>117554</t>
+          <t>124876</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104198</t>
+          <t>112019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132100</t>
+          <t>139221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>264919</t>
+          <t>268939</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238926</t>
+          <t>244110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291747</t>
+          <t>292124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>310703</t>
+          <t>318097</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>310703</t>
+          <t>318097</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>310703</t>
+          <t>318097</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287192</t>
+          <t>312701</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287192</t>
+          <t>312701</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287192</t>
+          <t>312701</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>597896</t>
+          <t>630798</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>597896</t>
+          <t>630798</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>597896</t>
+          <t>630798</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>325402</t>
+          <t>332329</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>293993</t>
+          <t>303386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>353412</t>
+          <t>357722</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>293936</t>
+          <t>313655</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274217</t>
+          <t>290910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313314</t>
+          <t>333724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>619338</t>
+          <t>645984</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>580976</t>
+          <t>611231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>653247</t>
+          <t>682333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>188535</t>
+          <t>192622</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160525</t>
+          <t>167229</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219944</t>
+          <t>221565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>219129</t>
+          <t>230914</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199751</t>
+          <t>210845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238848</t>
+          <t>253659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>407664</t>
+          <t>423536</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>373755</t>
+          <t>387187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>446026</t>
+          <t>458289</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>513937</t>
+          <t>524951</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513937</t>
+          <t>524951</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>513937</t>
+          <t>524951</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513065</t>
+          <t>544569</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513065</t>
+          <t>544569</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513065</t>
+          <t>544569</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1027002</t>
+          <t>1069520</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1027002</t>
+          <t>1069520</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1027002</t>
+          <t>1069520</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>138011</t>
+          <t>140615</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121539</t>
+          <t>125559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154293</t>
+          <t>156876</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>166443</t>
+          <t>174779</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151130</t>
+          <t>160105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181618</t>
+          <t>192622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>304454</t>
+          <t>315394</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>282785</t>
+          <t>292994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>324860</t>
+          <t>339943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>168771</t>
+          <t>166450</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152489</t>
+          <t>150189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>185243</t>
+          <t>181506</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>162015</t>
+          <t>162669</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146840</t>
+          <t>144826</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177328</t>
+          <t>177343</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>330785</t>
+          <t>329119</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310379</t>
+          <t>304570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352454</t>
+          <t>351519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>54,54%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>306782</t>
+          <t>307065</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>306782</t>
+          <t>307065</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>306782</t>
+          <t>307065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>328458</t>
+          <t>337448</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>328458</t>
+          <t>337448</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>328458</t>
+          <t>337448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>635239</t>
+          <t>644513</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>635239</t>
+          <t>644513</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>635239</t>
+          <t>644513</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>99386</t>
+          <t>121529</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81025</t>
+          <t>101469</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121919</t>
+          <t>147004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>133284</t>
+          <t>150812</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80601</t>
+          <t>132594</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170080</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>232670</t>
+          <t>272340</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176614</t>
+          <t>241895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273690</t>
+          <t>302926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>209028</t>
+          <t>245390</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186495</t>
+          <t>219915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227389</t>
+          <t>265450</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>332347</t>
+          <t>260446</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295551</t>
+          <t>242050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385030</t>
+          <t>278664</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>541375</t>
+          <t>505837</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>500355</t>
+          <t>475251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>597431</t>
+          <t>536282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>308414</t>
+          <t>366919</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>308414</t>
+          <t>366919</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>308414</t>
+          <t>366919</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>465631</t>
+          <t>411258</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>465631</t>
+          <t>411258</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>465631</t>
+          <t>411258</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>774045</t>
+          <t>778177</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>774045</t>
+          <t>778177</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>774045</t>
+          <t>778177</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>164606</t>
+          <t>188074</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155691</t>
+          <t>178853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170231</t>
+          <t>194723</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>192391</t>
+          <t>210496</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185531</t>
+          <t>202594</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197280</t>
+          <t>216000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>356997</t>
+          <t>398570</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>345129</t>
+          <t>387144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364362</t>
+          <t>407954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>26077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22743</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>29335</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>23799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41203</t>
+          <t>44609</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178058</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178058</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178058</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386332</t>
+          <t>431753</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386332</t>
+          <t>431753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386332</t>
+          <t>431753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>104155</t>
+          <t>109934</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91322</t>
+          <t>96294</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>118096</t>
+          <t>123450</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>101569</t>
+          <t>107371</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90361</t>
+          <t>95228</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>115085</t>
+          <t>119463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>205724</t>
+          <t>217305</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>187213</t>
+          <t>199306</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>222822</t>
+          <t>237049</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>165016</t>
+          <t>160296</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151075</t>
+          <t>146780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177849</t>
+          <t>173936</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>155094</t>
+          <t>155970</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>141578</t>
+          <t>143878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166302</t>
+          <t>168113</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>320110</t>
+          <t>316265</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>303012</t>
+          <t>296521</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>338621</t>
+          <t>334264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>62,65%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269171</t>
+          <t>270230</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269171</t>
+          <t>270230</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269171</t>
+          <t>270230</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256663</t>
+          <t>263341</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256663</t>
+          <t>263341</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256663</t>
+          <t>263341</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525834</t>
+          <t>533570</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525834</t>
+          <t>533570</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525834</t>
+          <t>533570</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,102 +12755,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>377145</t>
+          <t>444261</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>347120</t>
+          <t>412812</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>406737</t>
+          <t>473324</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>66,75%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>483524</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>457377</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>506923</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>63,89%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>60,43%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>66,98%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>927784</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>890284</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>968892</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>63,29%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>60,73%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>66,1%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>398226</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>372366</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>421367</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>63,01%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>58,92%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>66,68%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>775371</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>735601</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>812529</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>62,17%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>58,98%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -12868,102 +12868,102 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>238163</t>
+          <t>264797</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208571</t>
+          <t>235734</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>268188</t>
+          <t>296246</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>33,25%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,78%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>273284</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>249885</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>299431</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>36,11%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>33,02%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>39,57%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>538082</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>496974</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>575582</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>33,9%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>43,59%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>233735</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>210594</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>259595</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>36,99%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>33,32%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>41,08%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>471897</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>434739</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>511667</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>37,83%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>615308</t>
+          <t>709058</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>615308</t>
+          <t>709058</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>615308</t>
+          <t>709058</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>631961</t>
+          <t>756808</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>631961</t>
+          <t>756808</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>631961</t>
+          <t>756808</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1247268</t>
+          <t>1465866</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1247268</t>
+          <t>1465866</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1247268</t>
+          <t>1465866</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>576572</t>
+          <t>672871</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>261141</t>
+          <t>649015</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>794057</t>
+          <t>694508</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>625741</t>
+          <t>723471</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>608526</t>
+          <t>703871</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>640598</t>
+          <t>741960</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1202314</t>
+          <t>1396343</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>738102</t>
+          <t>1364416</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1424370</t>
+          <t>1421779</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>349486</t>
+          <t>122237</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>132001</t>
+          <t>100600</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>664917</t>
+          <t>146093</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>90891</t>
+          <t>105894</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76034</t>
+          <t>87405</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>108106</t>
+          <t>125494</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>440377</t>
+          <t>228131</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>218321</t>
+          <t>202695</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>904589</t>
+          <t>260058</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926058</t>
+          <t>795108</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926058</t>
+          <t>795108</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926058</t>
+          <t>795108</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716632</t>
+          <t>829365</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716632</t>
+          <t>829365</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716632</t>
+          <t>829365</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1642691</t>
+          <t>1624474</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1642691</t>
+          <t>1624474</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1642691</t>
+          <t>1624474</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1948615</t>
+          <t>2183645</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1502962</t>
+          <t>2119131</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2115993</t>
+          <t>2243836</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2081228</t>
+          <t>2351934</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1933782</t>
+          <t>2299379</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2152435</t>
+          <t>2411260</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4029843</t>
+          <t>4535579</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3540564</t>
+          <t>4453342</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4221190</t>
+          <t>4622930</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1479816</t>
+          <t>1312712</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1312438</t>
+          <t>1252521</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1925469</t>
+          <t>1377226</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1326648</t>
+          <t>1330379</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1255441</t>
+          <t>1271053</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1474094</t>
+          <t>1382934</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2806464</t>
+          <t>2643091</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2615117</t>
+          <t>2555740</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3295743</t>
+          <t>2725328</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3428431</t>
+          <t>3496357</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3428431</t>
+          <t>3496357</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3428431</t>
+          <t>3496357</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3407876</t>
+          <t>3682313</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3407876</t>
+          <t>3682313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3407876</t>
+          <t>3682313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6836307</t>
+          <t>7178670</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6836307</t>
+          <t>7178670</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6836307</t>
+          <t>7178670</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
